--- a/Data_Coverage_Dashboard.xlsx
+++ b/Data_Coverage_Dashboard.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Location_Hierarchy_Sources'!$A$1:$E$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ward_Data_Quality'!$A$1:$C$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Complaint_Ward_Text_Quality'!$A$1:$C$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'RAG_City_Breakdown'!$A$1:$E$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'RAG_City_Breakdown'!$A$1:$E$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9">
@@ -1134,25 +1134,25 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1162,9 +1162,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr">
@@ -1438,19 +1438,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1466,9 +1466,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R11" s="5" t="inlineStr">
@@ -5256,7 +5256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5434,16 +5434,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -5462,76 +5462,76 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Mostly synthetic</t>
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Mostly synthetic</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>(state-wide record)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Faridabad</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -5549,12 +5549,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -5572,35 +5572,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Faridabad</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Mostly synthetic</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mysuru</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -5618,35 +5618,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
         <v>4</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Mostly synthetic</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>Mysuru</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -5664,46 +5664,46 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>(state-wide record)</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>100% real</t>
+        <v>4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>Thiruvananthapuram</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
         <v>4</v>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>100% SYNTHETIC -- 0 real records</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
@@ -5715,53 +5715,53 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>(state-wide record)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>4</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>100% SYNTHETIC -- 0 real records</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -5779,62 +5779,62 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>(state-wide record)</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>100% real</t>
+        <v>4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Patiala</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>100% real</t>
+        <v>4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar (Mohali)</t>
+          <t>(state-wide record)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -5848,58 +5848,58 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Patiala</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+        <v>0</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jodhpur</t>
+          <t>Sahibzada Ajit Singh Nagar (Mohali)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -5917,16 +5917,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Jodhpur</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
         <v>4</v>
@@ -5940,16 +5940,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
         <v>4</v>
@@ -5963,16 +5963,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Warangal</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
         <v>4</v>
@@ -5986,16 +5986,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
         <v>4</v>
@@ -6009,12 +6009,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Warangal</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -6032,35 +6032,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>(state-wide record)</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>100% real</t>
+        <v>4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Howrah</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -6083,23 +6083,69 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>(state-wide record)</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Howrah</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>Kolkata</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C38" t="n">
         <v>4</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D38" t="n">
         <v>4</v>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Mostly real</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E36"/>
+  <autoFilter ref="A1:E38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Data_Coverage_Dashboard.xlsx
+++ b/Data_Coverage_Dashboard.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Location_Hierarchy_Sources'!$A$1:$E$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ward_Data_Quality'!$A$1:$C$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Complaint_Ward_Text_Quality'!$A$1:$C$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'RAG_City_Breakdown'!$A$1:$E$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'RAG_City_Breakdown'!$A$1:$E$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9">
@@ -1456,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1818,25 +1818,25 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -1846,9 +1846,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R16" s="5" t="inlineStr">
@@ -3338,13 +3338,13 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -3366,9 +3366,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q36" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R36" s="5" t="inlineStr">
@@ -5256,7 +5256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -5618,23 +5618,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Ranchi</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Mostly synthetic</t>
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
@@ -5646,30 +5646,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mysuru</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
         <v>4</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Mostly synthetic</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Mysuru</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -5710,23 +5710,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>(state-wide record)</t>
+          <t>Thiruvananthapuram</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>100% real</t>
+        <v>4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
@@ -5738,18 +5738,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>(state-wide record)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>100% SYNTHETIC -- 0 real records</t>
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
@@ -5761,34 +5761,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>4</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>100% SYNTHETIC -- 0 real records</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
         <v>4</v>
@@ -5807,11 +5807,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
         <v>4</v>
@@ -5825,39 +5825,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>(state-wide record)</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>100% real</t>
+        <v>4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Patiala</t>
+          <t>(state-wide record)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar (Mohali)</t>
+          <t>Patiala</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -5894,23 +5894,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Sahibzada Ajit Singh Nagar (Mohali)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+        <v>0</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Jodhpur</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5940,12 +5940,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Jodhpur</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -5968,11 +5968,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
         <v>4</v>
@@ -5986,12 +5986,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -6014,11 +6014,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Warangal</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
         <v>4</v>
@@ -6032,12 +6032,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Warangal</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -6078,46 +6078,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>(state-wide record)</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>100% real</t>
+        <v>4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Howrah</t>
+          <t>Dehradun</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+        <v>0</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
@@ -6129,23 +6129,69 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>(state-wide record)</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Howrah</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>Kolkata</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C40" t="n">
         <v>4</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D40" t="n">
         <v>4</v>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Mostly real</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E38"/>
+  <autoFilter ref="A1:E40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Data_Coverage_Dashboard.xlsx
+++ b/Data_Coverage_Dashboard.xlsx
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9">
@@ -3350,7 +3350,7 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -6110,7 +6110,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>

--- a/Data_Coverage_Dashboard.xlsx
+++ b/Data_Coverage_Dashboard.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Location_Hierarchy_Sources'!$A$1:$E$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ward_Data_Quality'!$A$1:$C$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Complaint_Ward_Text_Quality'!$A$1:$C$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'RAG_City_Breakdown'!$A$1:$E$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'RAG_City_Breakdown'!$A$1:$E$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9">
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1238,9 +1238,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R8" s="5" t="inlineStr">
@@ -1666,25 +1666,25 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1694,9 +1694,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q14" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R14" s="5" t="inlineStr">
@@ -2730,13 +2730,13 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2758,9 +2758,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q28" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R28" s="5" t="inlineStr">
@@ -5256,7 +5256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5457,16 +5457,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Raipur</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -5485,64 +5485,64 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Mostly synthetic</t>
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>(state-wide record)</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
         <v>4</v>
       </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>100% real</t>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Mostly synthetic</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>(state-wide record)</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -5572,12 +5572,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Faridabad</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Faridabad</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -5618,104 +5618,104 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ranchi</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>100% real</t>
+        <v>4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Shimla</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>Mostly synthetic</t>
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mysuru</t>
+          <t>Ranchi</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
         <v>4</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Mostly synthetic</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>Mysuru</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -5733,46 +5733,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>(state-wide record)</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>100% real</t>
+        <v>4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>Thiruvananthapuram</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
         <v>4</v>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>100% SYNTHETIC -- 0 real records</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
@@ -5784,53 +5784,53 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>(state-wide record)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>4</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>100% SYNTHETIC -- 0 real records</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -5848,62 +5848,62 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>(state-wide record)</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>100% real</t>
+        <v>4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Patiala</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>100% real</t>
+        <v>4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar (Mohali)</t>
+          <t>(state-wide record)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -5917,85 +5917,85 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Puducherry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Oulgaret</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jodhpur</t>
+          <t>Patiala</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+        <v>0</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Sahibzada Ajit Singh Nagar (Mohali)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
         <v>4</v>
@@ -6009,16 +6009,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Jodhpur</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
         <v>4</v>
@@ -6032,12 +6032,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Warangal</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -6055,16 +6055,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
         <v>4</v>
@@ -6078,16 +6078,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
         <v>4</v>
@@ -6101,58 +6101,58 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Uttarakhand</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dehradun</t>
+          <t>Warangal</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>100% real</t>
+        <v>4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>(state-wide record)</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>100% real</t>
+        <v>4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Howrah</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -6170,28 +6170,97 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Dehradun</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>4</v>
       </c>
       <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>(state-wide record)</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Howrah</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
         <v>4</v>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="D42" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>Mostly real</t>
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E40"/>
+  <autoFilter ref="A1:E43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Data_Coverage_Dashboard.xlsx
+++ b/Data_Coverage_Dashboard.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Location_Hierarchy_Sources'!$A$1:$E$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ward_Data_Quality'!$A$1:$C$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Complaint_Ward_Text_Quality'!$A$1:$C$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'RAG_City_Breakdown'!$A$1:$E$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'RAG_City_Breakdown'!$A$1:$E$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9">
@@ -1742,25 +1742,25 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1770,9 +1770,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Q15" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R15" s="5" t="inlineStr">
@@ -2742,13 +2742,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -5256,7 +5256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5664,12 +5664,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Jammu and Kashmir</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ranchi</t>
+          <t>Srinagar</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -5687,23 +5687,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Ranchi</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Mostly synthetic</t>
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
@@ -5715,30 +5715,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mysuru</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Mostly synthetic</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Mysuru</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Thiruvananthapuram</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -5779,23 +5779,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>(state-wide record)</t>
+          <t>Thiruvananthapuram</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>100% real</t>
+        <v>4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
@@ -5807,18 +5807,18 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bhopal</t>
+          <t>(state-wide record)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>100% SYNTHETIC -- 0 real records</t>
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
@@ -5830,34 +5830,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Indore</t>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>100% SYNTHETIC -- 0 real records</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Indore</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
         <v>4</v>
@@ -5876,11 +5876,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
         <v>4</v>
@@ -5894,39 +5894,39 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>(state-wide record)</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>100% real</t>
+        <v>4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Puducherry</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Oulgaret</t>
+          <t>(state-wide record)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -5940,16 +5940,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Puducherry</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Patiala</t>
+          <t>Oulgaret</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sahibzada Ajit Singh Nagar (Mohali)</t>
+          <t>Patiala</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -5986,23 +5986,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Sahibzada Ajit Singh Nagar (Mohali)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+        <v>0</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jodhpur</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -6032,12 +6032,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Jodhpur</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -6060,11 +6060,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Coimbatore</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
         <v>4</v>
@@ -6078,12 +6078,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -6106,11 +6106,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Warangal</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
         <v>4</v>
@@ -6124,12 +6124,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Warangal</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -6170,39 +6170,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Uttarakhand</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dehradun</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>100% real</t>
+        <v>4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>(state-wide record)</t>
+          <t>Dehradun</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -6221,18 +6221,18 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Howrah</t>
+          <t>(state-wide record)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Mostly real</t>
+        <v>0</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>100% real</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Howrah</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -6259,8 +6259,31 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Mostly real</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E43"/>
+  <autoFilter ref="A1:E44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Data_Coverage_Dashboard.xlsx
+++ b/Data_Coverage_Dashboard.xlsx
@@ -17,8 +17,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'State_Coverage_Matrix'!$A$1:$R$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Location_Hierarchy_Sources'!$A$1:$E$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ward_Data_Quality'!$A$1:$C$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Complaint_Ward_Text_Quality'!$A$1:$C$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ward_Data_Quality'!$A$1:$C$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Complaint_Ward_Text_Quality'!$A$1:$C$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'RAG_City_Breakdown'!$A$1:$E$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>3</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -4990,7 +4990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5018,46 +5018,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mitesh Patel</t>
+          <t>Debug Worker</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ward 11 — Navrangpura, Ahmedabad</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>Clean (matches seeded hierarchy)</t>
+          <t>Debug Ward 743579</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sunita Pawar</t>
+          <t>Evidence Test Worker</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ward 22 — Kothrud, Pune</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Clean (matches seeded hierarchy)</t>
+          <t>Evidence Test Ward 1786459064599</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Arjun Reddy</t>
+          <t>Evidence Test Worker</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ward 3 — Indiranagar, Bengaluru</t>
+          <t>Evidence Test Ward 1786459098935</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -5069,12 +5069,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Debasish Nayak</t>
+          <t>Evidence Test Worker</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ward 5 — Saheed Nagar, Bhubaneswar</t>
+          <t>Evidence Test Ward 1786479393410</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -5086,39 +5086,3422 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sourav Chatterjee</t>
+          <t>Evidence Test Worker</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ward 6 — Salt Lake, Kolkata</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Clean (matches seeded hierarchy)</t>
+          <t>Evidence Test Ward 1786479536233</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786479635778</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786479706597</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786479749073</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786479827326</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786479890909</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786479995368</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786480191369</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786480262049</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786480526963</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786480598552</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786480895803</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786481547316</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786481582716</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786481663316</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786481708898</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786481838880</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786481996227</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786488852176</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786503375929</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786504193573</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786533107230</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786533119848</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786533838057</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786536038927</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Evidence Test Worker</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786553483434</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786392423645</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786392423645 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786392495277</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786392495277 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786400585607</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786400621684</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786400621684 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786400698905</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786400698905 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786400773618</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786400773618 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786400890051</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786400890051 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786401080568</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786401080568 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786458542989</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786458542989 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786458557095</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786458557095 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786459195386</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786459195386 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786479839155</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786479839155 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786479872320</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786479872320 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786482047938</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786482047938 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786488910436</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786488910436 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786503452230</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786503452230 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786504295290</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786504295290 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786533186259</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786533186259 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786533203084</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786533203084 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786533929909</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786533929909 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786536094894</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786536094894 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Notif Worker</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786553534234</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Other Worker</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786553534234 (unrelated)</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Test Worker</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Test Ward 1786380458567</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Timing Worker</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Timing Test Ward 1786480395</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Track Worker One</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786392278570</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Track Worker Two</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786392278570</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Track Worker One</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786392350694</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Track Worker Two</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786392350694</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Track Worker One</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786400537049</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Track Worker Two</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786400537049</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Track Worker One</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786401005631</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Track Worker Two</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786401005631</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Track Worker One</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786457817530</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Track Worker Two</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786457817530</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Track Worker One</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786459006550</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Track Worker Two</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786459006550</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Track Worker One</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786479655663</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Track Worker Two</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786479655663</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Track Worker One</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786481955247</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Track Worker Two</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786481955247</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Track Worker One</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786488800358</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Track Worker Two</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786488800358</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Track Worker One</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786503265072</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Track Worker Two</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786503265072</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Track Worker One</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786504132849</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Track Worker Two</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786504132849</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Track Worker One</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786533063888</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Track Worker Two</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786533063888</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Track Worker One</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786533086744</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Track Worker Two</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786533086744</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Track Worker One</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786533707416</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Track Worker Two</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786533707416</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Track Worker One</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786533782840</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Track Worker Two</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786533782840</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Track Worker One</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786535982474</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Track Worker Two</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786535982474</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Track Worker One</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786553433602</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Track Worker Two</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786553433602</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Mitesh Patel</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Ward 11 — Navrangpura, Ahmedabad</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Clean (matches seeded hierarchy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786152369422</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786155190012</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786283296754</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786316899875</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786317394615</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786317658096</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786317827870</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786317959563</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786318070478</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786318200215</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786323587498</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786323737814</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786325986279</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786326108551</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786326135840</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786326346786</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786326458382</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786327439173</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786327781192</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786328121881</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786328231880</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786328330279</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786329021737</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786329904997</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786330945210</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786331838016</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786333048222</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786334201576</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786334492757</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786335117406</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786335514862</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786336186803</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786336920991</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786337584832</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786337770438</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786338388067</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786338770140</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786338869658</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786339115379</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786339536980</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786339807033</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786340341249</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786340835870</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786341389659</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786342417232</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786343001596</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786343233435</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786343453564</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786344528286</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786344741192</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786345645141</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786346321955</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786346719635</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786347230117</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786348515217</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786349624237</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786352452205</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786352865010</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786352996445</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786353325668</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786353716616</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786357225851</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786357726417</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786358345520</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786359054799</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786359687508</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786360126147</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786360394931</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786360651118</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786361100172</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786361263986</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786362335921</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786365418410</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786366870880</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786370987612</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786392259524</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786400961001</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786457740994</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786458939786</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786479602688</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786481897688</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786488746035</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786502729724</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786503555828</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786532194479</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786533365143</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786535201011</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Ramesh Kadam</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road 1786553108245</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Sunita Pawar</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Ward 22 — Kothrud, Pune</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="inlineStr">
+        <is>
+          <t>Clean (matches seeded hierarchy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Arjun Reddy</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Ward 3 — Indiranagar, Bengaluru</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Debasish Nayak</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Ward 5 — Saheed Nagar, Bhubaneswar</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Sourav Chatterjee</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Ward 6 — Salt Lake, Kolkata</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t>Clean (matches seeded hierarchy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
           <t>Rajesh Kumar</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B205" t="inlineStr">
         <is>
           <t>Ward 8 — Civil Lines, Kanpur</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK (not a real place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Suresh Jadhav</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Ward 9 — Shivaji Nagar</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
         <is>
           <t>TEST-FIXTURE JUNK (not a real place)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C7"/>
+  <autoFilter ref="A1:C206"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5129,7 +8512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5157,41 +8540,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ward 11 — Navrangpura, Ahmedabad</t>
+          <t>Debug Ward 743579</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>Clean (matches seeded hierarchy)</t>
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ward 22 — Kothrud, Pune</t>
+          <t>Evidence Test Ward 1786459064599</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Clean (matches seeded hierarchy)</t>
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ward 3 — Indiranagar, Bengaluru</t>
+          <t>Evidence Test Ward 1786459098935</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -5202,11 +8585,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ward 5 — Saheed Nagar, Bhubaneswar</t>
+          <t>Evidence Test Ward 1786479393410</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -5217,35 +8600,920 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ward 6 — Salt Lake, Kolkata</t>
+          <t>Evidence Test Ward 1786479536233</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Clean (matches seeded hierarchy)</t>
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Evidence Test Ward 1786479706597</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786479749073</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786479827326</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786479995368</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786480191369</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786480262049</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786480526963</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786480598552</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786480895803</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786481547316</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786481582716</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786481663316</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786481708898</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786481838880</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786481996227</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786488852176</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786503375929</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786504193573</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786533838057</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786536038927</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Evidence Test Ward 1786553483434</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Mohali</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786392423645</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786400585607</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786400621684</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786400698905</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786400773618</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786400890051</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786401080568</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786459195386</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786479872320</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786482047938</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786488910436</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786503452230</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786504295290</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786533929909</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786536094894</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Notif Test Ward 1786553534234</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Timing Test Ward 1786480395</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786400537049</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786401005631</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786457817530</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786459006550</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786479655663</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786481955247</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786488800358</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786503265072</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786504132849</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786533782840</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786535982474</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Tracking Test Ward 1786553433602</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Ward 11 — Navrangpura, Ahmedabad</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Clean (matches seeded hierarchy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ward 14</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Ward 14 — Rukadi Road</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ward 15 — Rukadi Road</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Ward 22 — Kothrud, Pune</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Clean (matches seeded hierarchy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Ward 3 — Indiranagar, Bengaluru</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>5</v>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Ward 5 — Saheed Nagar, Bhubaneswar</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>5</v>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Ward 6 — Salt Lake, Kolkata</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>3</v>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Clean (matches seeded hierarchy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>Ward 8 — Civil Lines, Kanpur</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>28</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B66" t="n">
+        <v>5</v>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>TEST-FIXTURE JUNK / inconsistent (not a real, canonical place string)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C7"/>
+  <autoFilter ref="A1:C66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
